--- a/docentes/Sánchez Sánchez Miguel - Estadisticos 20232.xlsx
+++ b/docentes/Sánchez Sánchez Miguel - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -76,40 +76,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>MORALES</t>
+    <t>MONTALVO</t>
   </si>
   <si>
     <t>SOTO</t>
   </si>
   <si>
-    <t>GALINDO</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
+    <t>DIANA IRAIS</t>
   </si>
   <si>
     <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>BRANDON</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>ALDO</t>
   </si>
 </sst>
 </file>
@@ -627,16 +609,19 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>91.3</v>
+      </c>
+      <c r="H2">
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -650,16 +635,19 @@
         <v>23</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>95.65000000000001</v>
+      </c>
+      <c r="H3">
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -673,16 +661,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>76.19</v>
+      </c>
+      <c r="H4">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -747,7 +738,7 @@
         <v>91.3</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -764,16 +755,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>91.3</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -790,16 +781,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>57.14</v>
+        <v>76.19</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -809,7 +800,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -841,16 +832,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920396</v>
+        <v>21330051920117</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
         <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -864,16 +855,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920395</v>
+        <v>21330051920396</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
         <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>28</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -882,52 +873,6 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920117</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920272</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Sánchez Sánchez Miguel - Estadisticos 20232.xlsx
+++ b/docentes/Sánchez Sánchez Miguel - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="19">
   <si>
     <t>Mat</t>
   </si>
@@ -74,24 +74,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
   </si>
 </sst>
 </file>
@@ -729,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>91.3</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -764,7 +746,7 @@
         <v>95.65000000000001</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -781,13 +763,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>76.19</v>
+        <v>90.48</v>
       </c>
       <c r="H4">
         <v>7.3</v>
@@ -800,7 +782,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -830,52 +812,6 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920117</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920396</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
